--- a/sponsorship_form_templates/012_public_policy_panel_sponsorship_form--sponsorship_form_templates.xlsx
+++ b/sponsorship_form_templates/012_public_policy_panel_sponsorship_form--sponsorship_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'sponsor'}</t>
+          <t>sponsor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Sponsor'}</t>
+          <t>Sponsor</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'partner'}</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Partner'}</t>
+          <t>Partner</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Individual'}</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Organization'}</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'usd'}</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'USD'}</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'eur'}</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'EUR'}</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'monetary_support'}</t>
+          <t>monetary_support</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Monetary Support'}</t>
+          <t>Monetary Support</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'product/service'}</t>
+          <t>product/service</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Product/Service'}</t>
+          <t>Product/Service</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'one-time_payment'}</t>
+          <t>one-time_payment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'One-time payment'}</t>
+          <t>One-time payment</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'ongoing_payment'}</t>
+          <t>ongoing_payment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Ongoing payment'}</t>
+          <t>Ongoing payment</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
